--- a/docs/accounts/eco/pilot-test-03-eco2-tracking.xlsx
+++ b/docs/accounts/eco/pilot-test-03-eco2-tracking.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -107,6 +127,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,100 +526,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Группа</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Вопрос</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Статус 11.09 (пилот)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Статус 12.09 (ре-тест eco)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Дата — проход A</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ответ — проход A (Данные+SQL+Документы)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Источник(и) — проход A</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Статус — проход A</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Дата — проход B</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Ответ — проход B (только Документы)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Источник(и) — проход B</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Статус — проход B</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Итоговый вывод</t>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Статус 11.09</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус 12.09</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Коллекция</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ (кратко)</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Источник — в тексте</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Источник — в карточке</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>Совпадает?</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>Статус (12.09.2026)</t>
         </is>
       </c>
     </row>
@@ -576,31 +612,56 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Я начальник склада. Мне принесли акт забраковки. Что я должен сделать?</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Я начальник склада. Мне принесли акт забраковки. Что я должен сделать?</t>
+          <t>Чёткий ответ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Чёткий ответ</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
           <t>Без изменений — верно (не была ошибкой)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Верно — 4 шага (Форма 03-01, зона «БРАК» ≤1 раб.дня, размещение по акту, перемещение в 1С-8)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ПР-03-00-12 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>ПР-03-00-12 (для теста ИИ), 58%</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -609,31 +670,56 @@
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Я технолог ЛР. Кто управляет процессом, когда мы делаем экспериментальную партию?</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Я технолог ЛР. Кто управляет процессом, когда мы делаем экспериментальную партию?</t>
+          <t>Нет чёткого ответа</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Нет чёткого ответа</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
           <t>Исправлено</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Верно — технолог лаборатории руководит</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>И-16-01-11 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>И-16-01-11 (для теста ИИ), 43%</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>Исправлено (vs 11.09)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -642,566 +728,1332 @@
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Я мастер на производстве. В заказе увидел пометку «Экспериментальная». Мои действия?</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Я мастер на производстве. В заказе увидел пометку «Экспериментальная». Мои действия?</t>
+          <t>Частичный ответ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Частичный ответ</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
           <t>Исправлено</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>РЕГРЕССИЯ — «не найдено», источник не по теме</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (для теста ИИ), 57%</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Регрессия vs 12.09</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Я мастер на производстве. В заказе увидел пометку «Экспериментальная». Мои действия?</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Исправлено</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО_2</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Верно — 3 шага (запрос Руководителю ЛР, копия технологу ПО)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>И-16-01-11 (eco-converted, ЭКО_2)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>«глоссарий», 100%</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — аномалия</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>Исправлено на ЭКО_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Какие поля заполняет оператор после фасовки продукции?</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Чёткий ответ</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Регрессия</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Верно — 4 поля (Кол-во тарных мест, Общее кол-во, Дата, Фасовщик)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>И-08-02-10 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>И-15-06-08 (для теста ИИ), 73%</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — аномалия</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно + аномалия</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>★ ПЕРВООЧЕРЕДНО</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Действия по корректировке Заказа на производство при выпуске продукции с меньшим весом.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Частичный ответ</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Без изменений — ошибка сохраняется</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>Источник Д-08-04-01 уже в корпусе, но не цитировался 12.09 — проверить, подтянется ли на чистой коллекции.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>★ ПЕРВООЧЕРЕДНО</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>С какой высоты нужно сбрасывать пластиковую тару объёмом от 1,5 до 5 литров, чтобы проверить её прочность?</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Нет чёткого ответа</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Частично — общая процедура через И-12-10-03, Д-08-04-01 не найден</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (для теста ИИ), 65%</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Без изменений — ошибка сохраняется</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>Ответ (0,8 м) должен быть в metodika-38.docx — точно читаемый файл; плюс здесь была 2-я аномалия цитирования («глоссарий»).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Действия по корректировке Заказа на производство при выпуске продукции с меньшим весом.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО_2</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО — 8 шагов именно из Д-08-04-01</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Д-08-04-01 (eco-converted, ЭКО_2)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Д-08-04-01 (eco-converted, ЭКО_2), 46%</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>Исправлено на ЭКО_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Как технолог ПО получает сырьё на производство?</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Чёткий ответ</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Без изменений — верно (не была ошибкой)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>★ ПЕРВООЧЕРЕДНО</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Я менеджер по продажам. Клиент попросил поменять характеристику товара в уже оформленном заказе, но на складе уже распечатали заявку на сборку. Что делать?</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Частичный ответ</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Частично улучшено</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>Источник И-12-10-03 отсутствовал в корпусе 12.09, теперь добавлен — прямая проверка гипотезы «формат/парсинг».</t>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>С какой высоты нужно сбрасывать пластиковую тару объёмом от 1,5 до 5 литров, чтобы проверить её прочность?</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Нет чёткого ответа</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО — 0,8 м дано верно</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Методика №38 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>«глоссарий», 100%</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — аномалия</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>Исправлено + аномалия</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>С какой высоты нужно сбрасывать пластиковую тару объёмом от 1,5 до 5 литров, чтобы проверить её прочность?</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Продукцию забраковали на производстве, кто и какие действия должен совершить?</t>
+          <t>Нет чёткого ответа</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Чёткий ответ</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Без изменений — верно (не была ошибкой)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
+          <t>Без изменений — ошибка сохраняется</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО (скоуп подтверждён)</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>То же — 0,8 м верно, скоуп подтверждён скриншотом</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Методика №38 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>«глоссарий», 100% — опять</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — аномалия</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>Аномалия воспроизведена при верном скоупе</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Как технолог ПО получает сырьё на производство?</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Какой маркой стретч-плёнки обматывают паллеты с готовой продукцией?</t>
+          <t>Чёткий ответ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Нет чёткого ответа</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
           <t>Без изменений — верно (не была ошибкой)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Верно — 6 шагов получения сырья</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Д-08-07-01 + ПР-08-00-14 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Д-08-07-01 (для теста ИИ), 55%</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Я менеджер по продажам. Клиент попросил поменять характеристику товара в уже оформленном заказе, но на складе уже распечатали заявку на сборку. Что делать?</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Как часто нужно оценивать квалификацию внештатных сотрудников, которые работают по договору подряда?</t>
+          <t>Частичный ответ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Нет чёткого ответа</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Без изменений — верно (не была ошибкой)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+          <t>Частично улучшено</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Частично — деталь про распечатанную заявку не всплывает</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (для теста ИИ), 70%</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>Частично улучшено (как на 12.09)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Я менеджер по продажам. Клиент попросил поменять характеристику товара в уже оформленном заказе, но на складе уже распечатали заявку на сборку. Что делать?</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Какие поля должны быть заполнены в журнале «Учёт уборки производственного оборудования» Форма 17-08?</t>
+          <t>Частичный ответ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Нет чёткого ответа</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Без изменений — верно (не была ошибкой)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
+          <t>Частично улучшено</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО_2</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Существенно улучшено — конкретная процедура (репринт заявки)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 + И-12-12-06 (частично eco-converted)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03 (eco-converted, ЭКО_2), 45%</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>Улучшено на ЭКО_2 (не дословно как предсказано)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Продукцию забраковали на производстве, кто и какие действия должен совершить?</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Чёткий ответ</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — верно (не была ошибкой)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Верно, детальнее — 5 шагов + ветка «акт передан на склад»</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>И-08-03-09 + ПР-03-00-12 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Обе карточки совпадают, 60%+60%</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Я технолог производства. Необходимое сырьё находится на складе «Проверка ОКК». Как мне его получить?</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Частичный ответ</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Исправлено</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>★ ПЕРВООЧЕРЕДНО</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Я механик. Пришло несколько заявок на срочный ремонт. Как понять, какую делать первой?</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Частичный ответ</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Без изменений — ошибка сохраняется (retrieval, контрольный случай)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>Контрольный retrieval-случай — источник читаемый и полный, если не найдётся и здесь, проблема точно не в формате файлов.</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Какой маркой стретч-плёнки обматывают паллеты с готовой продукцией?</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Нет чёткого ответа</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — верно (не была ошибкой)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Верное «не найдено» — марка физически не в корпусе</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Д-09-01-17 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Д-09-01-17 (для теста ИИ), 52%</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верное «не найдено»</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Какой маркой стретч-плёнки обматывают паллеты с готовой продукцией?</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Я начальник производства. Нужно сделать запас продукции на склад, но оборудование занято под срочный заказ покупателя. Как поступить?</t>
+          <t>Нет чёткого ответа</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Чёткий ответ</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
           <t>Без изменений — верно (не была ошибкой)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО_2</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>То же верное «не найдено», консистентно</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>forma-09-01 (eco-converted, ЭКО_2)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>forma-09-01 (eco-converted, ЭКО_2), 46%</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>Консистентно на обеих коллекциях</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Как часто нужно оценивать квалификацию внештатных сотрудников, которые работают по договору подряда?</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Какие действия оператора по фасовке готовой продукции?</t>
+          <t>Нет чёткого ответа</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Чёткий ответ</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
           <t>Без изменений — верно (не была ошибкой)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — периодичность не установлена, открытый вопрос</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ПР-14-00-12 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>ПР-14-00-12 (для теста ИИ), 48%</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
+          <t>Без изменений — открытый вопрос</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>★ ПЕРВООЧЕРЕДНО</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Как добавить новую Спецификацию в 1С-8?</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Частичный ответ</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Без изменений — ошибка сохраняется (+ служебная ошибка сервиса)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>Нужный источник И-08-05-08 в корпусе есть, но ни разу не подтягивался — плюс здесь была служебная ошибка сервиса, нужно перепроверить отдельно от неё.</t>
+      <c r="A18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Какие поля должны быть заполнены в журнале «Учёт уборки производственного оборудования» Форма 17-08?</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Нет чёткого ответа</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — верно (не была ошибкой)</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Верное «не найдено» — форма как бланк не в корпусе</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>И-08-04-13 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Д-11-06-01 + ПР-03-00-12 (для теста ИИ) — оба неверные</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — двойная аномалия</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верное «не найдено» + аномалия</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Я технолог производства. Необходимое сырьё находится на складе «Проверка ОКК». Как мне его получить?</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Исправлено</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Верно — 3 шага получения сырья со склада «Проверка ОКК»</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>ПР-09-00-14 + ПР-03-00-12 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Только ПР-03-00-12, 65% (2-й источник не показан)</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>Частично — неполнота</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно + неполная карточка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Я механик. Пришло несколько заявок на срочный ремонт. Как понять, какую делать первой?</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется (retrieval, контрольный случай)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>ПРОВАЛ — 3 источника не по теме, нужный документ не в топ-3</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>И-12-10-03, И-12-12-06, И-08-02-10 (для теста ИИ) — все неверные</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется (контрольный случай)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Я механик. Пришло несколько заявок на срочный ремонт. Как понять, какую делать первой?</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется (retrieval, контрольный случай)</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО_2</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО впервые за всю историю — верная процедура приоритизации</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ПР-10(02)-00 (eco-converted, ЭКО_2)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Д-17-12-03 (eco-converted), 46% — не тот файл</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — аномалия</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО на ЭКО_2 (n=1/1 на тот момент)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Я начальник производства. Нужно сделать запас продукции на склад, но оборудование занято под срочный заказ покупателя. Как поступить?</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Чёткий ответ</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — верно (не была ошибкой)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Верно, детальнее — 5 шагов планирования запаса</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>И-08-08-01 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>И-12-12-06 + Д-11-06-01 (для теста ИИ) — оба неверные</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — аномалия</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно + аномалия</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Какие действия оператора по фасовке готовой продукции?</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Чёткий ответ</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — верно (не была ошибкой)</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Верно, детальнее — 9 шагов (до/во время/после фасовки)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>И-08-02-10 + ПР-08-00-14 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Обе карточки совпадают, 57%+52%</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Как добавить новую Спецификацию в 1С-8?</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется (+ служебная ошибка сервиса)</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Частично — email-процедура, интерфейсные шаги 1С-8 не даны</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Д-08-03-01 (для теста ИИ) — не тот документ</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Д-08-03-01 (для теста ИИ), 61%</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>Да (но не тот документ!)</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Как добавить новую Спецификацию в 1С-8?</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Частичный ответ</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Без изменений — ошибка сохраняется (+ служебная ошибка сервиса)</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО_2</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО — полная 7-шаговая процедура именно из И-08-05-08</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>И-08-05-08 (eco-converted, ЭКО_2)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>И-08-05-08 (eco-converted, ЭКО_2), 51%</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО на ЭКО_2 (n=2/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Опиши процесс входного контроля сырья.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Чёткий ответ</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Без изменений — верно (не была ошибкой)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>ЭКО</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Верно, детальнее — 5 шагов входного контроля (журнал ф.09-01)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>ПР-09-00-14 + ПР-03-00-12 (для теста ИИ)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Блок карточек ПУСТ</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>НЕТ — карточка отсутствует</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>Без изменений — верно + аномалия (пустая карточка)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1214,7 +2066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1381,7 +2233,24 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Обновлено 12.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Полный прогон 18/18 вопросов выполнен, коллекция ЭКО (Closed-book RAG системный), с точечными перепроверками на ЭКО_2 для 1.3/2.2/3.2/4.1/5.2/6.2. Подробности — pilot-test-03-eco2-protocol.md.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/accounts/eco/pilot-test-03-eco2-tracking.xlsx
+++ b/docs/accounts/eco/pilot-test-03-eco2-tracking.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="70" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -604,6 +605,11 @@
           <t>Статус (12.09.2026)</t>
         </is>
       </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>Финальный ответ платформы (полный текст)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -662,6 +668,16 @@
           <t>Без изменений — верно</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Как начальник склада вы должны:
+1. Организовать маркировку несоответствующих ТМЦ актом забраковки ТМЦ — форма 03-01. Упакованную паллету можно промаркировать четырьмя актами, разместив их с каждой стороны паллеты.
+2. Переместить ТМЦ в зону «БРАК» не позднее одного рабочего дня с момента получения акта.
+3. Разместить забракованные ТМЦ в соответствии с требованиями, указанными в акте забраковки. Продукцию, содержащую аллерген, размещают в зоне «БРАК_Аллерген».
+4. Перемещение ТМЦ на склад «БРАК» в базе 1С-8 организует бухгалтер по учёту ТМЦ.
+Источник: ПР-03-00-12 «Несоответствующая продукция», п. 5.7.4–5.7.5.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -720,6 +736,13 @@
           <t>Исправлено (vs 11.09)</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Процессом экспериментальной выработки управляет Технолог лаборатории: он руководит производственным процессом и при необходимости вносит корректировки в процесс производства, отражая их в РИ (форма 16-03).
+При отклонении показателей качества от нормируемых продукт дорабатывается под руководством Технолога лаборатории.
+Источник: И-16-01-11 «Внедрение новых видов продукции в производство», фрагмент с обязанностями Технолога лаборатории: «руководит производственным процессом на экспериментальной выработке».</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -778,6 +801,12 @@
           <t>Регрессия vs 12.09</t>
         </is>
       </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>В доступных источниках не нашёл инструкции, которая описывает действия мастера производства именно при пометке «Экспериментальная» в заказе. Найденный фрагмент касается проверки изменений заказа в 1С и не содержит порядка действий для экспериментальной партии.
+Источник найденного фрагмента: И-12-10-03 «Корректировка Заказу покупателя в 1С».</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -836,6 +865,16 @@
           <t>Исправлено на ЭКО_2</t>
         </is>
       </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Процессом экспериментальной выработки управляет Технолог лаборатории: он руководит производственным процессом и при необходимости вносит корректировки в процесс производства, отражая их в РИ (форма 16-03).
+Также:
+— Ведущий технолог ПО фиксирует в РИ отличия действий оператора и/или количества загруженных ингредиентов.
+— После выработки образец передаётся в ОКК для проверки качества.
+— При отклонении показателей качества продукт дорабатывается под руководством Технолога лаборатории.
+Источник: И-16-01/11, цитата: «Технолог лаборатории — руководит производственным процессом на экспериментальной выработке».</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -894,6 +933,16 @@
           <t>Без изменений — верно + аномалия</t>
         </is>
       </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>После завершения фасовки оператор ПО заполняет в «Рабочей инструкции на производство» (форма 16-03):
+— «Кол-во тарных мест» — фактическое количество расфасованного продукта в штуках для каждого вида характеристики номенклатуры;
+— «Общее количество» — фактически расфасованное количество готового продукта в килограммах;
+— «Дата» — дата окончания фасовки;
+— «Фасовщик ФИО подпись» — ФИО и подпись сотрудника, который фасовал продукт.
+Источник: И-08-02-10 «Фасовка и упаковка готовой продукции», раздел «Заполнение "Рабочей инструкции на производство"».</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -952,6 +1001,16 @@
           <t>Без изменений — ошибка сохраняется</t>
         </is>
       </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>При выпуске продукции с меньшим весом:
+1. Откройте Заказ.
+2. Создайте корректировку к Заказу.
+3. В корректировке укажите количество, которое нужно убрать из Заказа, со знаком «−».
+4. Поскольку по заказу имеется Заказ на производство, для изменения продукта следует обратиться к ОБ.
+Источник: документ «И-12-10-03 Корректировка Заказу покупателя в 1С», таблица «Описание процесса оформления Заказа и Действий в Корректировке к Заказу в 1С». В найденном фрагменте отдельно не указано, как рассчитывать величину уменьшения именно в килограммах.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1010,6 +1069,20 @@
           <t>Исправлено на ЭКО_2</t>
         </is>
       </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>При сдаче заказа на производство с уменьшением веса:
+1. В «Заказе на производство» нажмите «Ввести на основании» → «Корректировка заказа на производство».
+2. На вкладке «Продукция и услуги»: в первой строке уменьшите количество готовой продукции на вес, равный тарному месту; во второй строке добавьте вес вскрытого тарного места без прикрепления к заказу покупателя.
+3. На вкладке «Материалы» удалите все строки.
+4. Проведите корректировку.
+5. В «Заказе на производство» нажмите «Анализ» и сверяйте получившийся вес с весом в форме 16-03 «Рабочая инструкция на производство».
+6. Далее заполните вкладку «Дополнительно»: укажите исполнителя, фактически использованное оборудование и дату исполнения заказа.
+7. Во вкладке «Процесс» установите отметку «Фасовка»; если не нажата кнопка «Выгрузка WMS», нажмите её.
+8. Заполните в форме 08-03 «Карточка выпуска готовой продукции» поле «раздел передачи готовой продукции с производства на склад».
+Источник: Д-08-04/01 «Проведение корректировок к заказу на производство в базе 1С-8 при сдаче готовой продукции на склад», пп. 3.4–3.5.6.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1068,6 +1141,12 @@
           <t>Исправлено + аномалия</t>
         </is>
       </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Для пластиковой тары объёмом свыше 1,5 до 5 л включительно высота падения должна быть не менее 0,8 м.
+Источник: Методика №38, «Высота падения, м, не менее: для значения свыше 1,5 до 5 включительно — 0,8».</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1126,6 +1205,12 @@
           <t>Аномалия воспроизведена при верном скоупе</t>
         </is>
       </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Для пластиковой тары объёмом свыше 1,5 до 5 литров включительно высота падения должна быть не менее 0,8 м.
+Источник: Методика №38, файл для теста ИИ (1)/Методика №38.doc: «Высота падения, м, не менее: для значения свыше 1,5 до 5 включительно — 0,8». (Повтор при явно подтверждённом скоупе: только Документы, SQL/каталог выключен, коллекция ЭКО.)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1184,6 +1269,17 @@
           <t>Без изменений — верно</t>
         </is>
       </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Технолог ПО получает сырьё так:
+1. Согласовывает с мастером ПО приоритетность задач на день.
+2. В 1С8 во вкладке «Процесс» соответствующего заказа устанавливает флажок «Передать сырьё» и нажимает «Выгрузить WMS».
+3. Дублирует запрос по телефону сотруднику СО, называя номера заказов и время, к которому нужно передать сырьё.
+4. После обратной связи от сотрудника СО о перемещении сырья забирает его на участке выдачи и перемещает к соответствующему оборудованию.
+Сырьё выдаётся на основании «Карточки выпуска готовой продукции» (форма 08-03), подписанной кладовщиком СО. При отсутствии в 1С8 отметки «Подбор сырья завершён» технолог ПО должен немедленно связаться по телефону с сотрудником СО, сообщить номер заказа о срочной сборке и передаче сырья, а затем проинформировать ответственного сотрудника ПО.
+Источник: Д-08-07/01 «Порядок получения ТМЦ с "Участка выдачи сырья" и сдача ТМЦ...», п. 5.1–5.4; ПР-08-00-14 «Производственный процесс», п. 5.4.4.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1242,6 +1338,17 @@
           <t>Частично улучшено (как на 12.09)</t>
         </is>
       </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Если заявка на комплектацию уже распечатана:
+1. Сообщите сотрудникам ОД и начальнику СО, что в заказ необходимо внести изменение.
+2. Откорректируйте заказ покупателя по И-12-10-03: откройте заказ и создайте корректировку; оставьте строку с исходной номенклатурой, которую нужно убрать; новой строкой добавьте ту же номенклатуру с требуемой характеристикой; при необходимости заполните материалы по спецификации и проведите корректировку.
+3. После внесения изменений уведомьте сотрудников ОД и начальника СО по электронной почте или телефону.
+4. Сотрудники ОД распечатают обновлённую заявку на комплектацию, передадут её в СО и повторно установят отметку «Заявка на комплектацию распечатана».
+Если по заказу уже создан заказ на производство, для изменения продукта нужно обратиться к ОБ.
+Источники: И-12-10-03 «Корректировка заказа покупателя в 1С»; И-12-12-06 «Оформление заказа покупателя».</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1300,6 +1407,16 @@
           <t>Улучшено на ЭКО_2 (не дословно как предсказано)</t>
         </is>
       </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Как начальник склада (СО), после получения акта забраковки вы должны:
+1. Организовать маркировку несоответствующих или потенциально небезопасных ТМЦ «Актом забраковки ТМЦ» (Форма 03-01). Упакованную паллету допускается маркировать четырьмя актами — по одному с каждой стороны.
+2. Переместить ТМЦ в складскую зону «БРАК» не позднее 1 рабочего дня с момента получения акта.
+3. Разместить забракованные ТМЦ в соответствии с требованиями, указанными в акте.
+Перемещение ТМЦ на склад «БРАК» в базе 1С-8 организует бухгалтер по учёту ТМЦ.
+Источник: инструкция 03-00-12, п. 5.7.4–5.7.5: «Начальник СО организует маркировку…» и «перемещение ТМЦ на складе в зону «БРАК», не позднее 1 рабочего дня…».</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1358,6 +1475,12 @@
           <t>Без изменений — верно</t>
         </is>
       </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Как начальник склада (СО), после получения акта забраковки вы должны: организовать маркировку несоответствующих ТМЦ (Форма 03-01), переместить их в зону «БРАК» не позднее 1 рабочего дня, разместить по требованиям акта.
+Источник: ПР-03-00-12, п. 5.7.4–5.7.5.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1416,6 +1539,17 @@
           <t>Без изменений — верное «не найдено»</t>
         </is>
       </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>При обнаружении забракованной продукции действуют так:
+1. Оператор ПО прекращает производство и сообщает Мастеру ПО и Технологу ПО. Если причина — попадание инородного предмета, выпуск также прекращается, а продукция считается потенциально небезопасной. Источник: И-08-03-09 «Действия при нештатных ситуациях».
+2. Мастер ПО: если продукция уже расфасована — организует её изоляцию; если продукция ещё не расфасована — сообщает Ведущему технологу ПО, Начальнику ПУ или Техническому директору. Источник: И-08-03-09, таблица №1.
+3. Решение о признании продукции несоответствующей принимает Руководитель ОКК / Директор по качеству. Результат фиксируется в соответствующем журнале, а также могут оформляться: Акт забраковки ТМЦ — форма 03-01; Акт разрешения на отклонение — форма 03-02; Акт на утилизацию — форма 03-04; запись в журнале «Учёт несоответствий продукции, сырья, тары» — форма 03-03. Источник: ПР-03-00-12 «Несоответствующая продукция».
+4. Ведущий технолог ПО действует согласно процедурам ПР-17-00 и ПР-03-00, а при необходимости сообщает группе БПП. Группа БПП действует согласно ПР-04-00. Источник: И-08-03-09, таблица №1.
+5. Решение о дальнейшем применении сырья и корректирующих действиях принимает Руководитель / Директор по качеству. Источник: ПР-03-00-12, таблица №1.
+Если акт уже передан на склад, начальник склада организует маркировку ТМЦ актом формы 03-01 и перемещение в зону «БРАК» не позднее одного рабочего дня; размещение выполняется по требованиям акта. Перемещение в 1С-8 организует бухгалтер по учёту ТМЦ. Источник: ПР-03-00-12, п. 5.7.4–5.7.5.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1474,6 +1608,12 @@
           <t>Консистентно на обеих коллекциях</t>
         </is>
       </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>В доступных источниках не нашёл указания на марку стретч-плёнки, которой обматывают паллеты с готовой продукцией.
+Источник найденного фрагмента — Д-09-01-17 «План контроля тары и упаковки», но в нём стретч-плёнка и её марка не указаны.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1532,6 +1672,12 @@
           <t>Без изменений — открытый вопрос</t>
         </is>
       </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>В доступных источниках не нашёл указания на марку стретч-плёнки для обмотки паллет с готовой продукцией.
+Источник проверенного документа — форма 09-01 «План контроля тары и упаковки», файл eco-converted-for-upload/forma-09-01-plan-kontrolya-tary-i-upakovki.docx: перечислены виды тары и упаковки, но стретч-плёнка и её марка не указаны.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1590,6 +1736,12 @@
           <t>Без изменений — верное «не найдено» + аномалия</t>
         </is>
       </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>В доступных источниках не нашёл указания, как часто нужно оценивать квалификацию внештатных сотрудников, работающих по договору подряда. Найденная процедура ПР-14-00-12 «Компетентность персонала» описывает оценку сотрудников, но найденные фрагменты не устанавливают периодичность для работников по договору подряда.
+Источник: ПР-14-00-12 «Компетентность персонала».</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1648,6 +1800,13 @@
           <t>Без изменений — верно + неполная карточка</t>
         </is>
       </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>В доступном фрагменте нет перечня полей журнала «Учёт уборки производственного оборудования» (форма 17-08).
+Найдено только, что форма 17-08 используется как чек-лист проверки ППУ и санитарного состояния производства, а еженедельный контроль состояния уборочного инвентаря проводит ответственный сотрудник ПО.
+Источник: И-08-04-13 «Уборка чистой зоны», фрагмент п. 4.4.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1706,6 +1865,16 @@
           <t>Без изменений — ошибка сохраняется (контрольный случай)</t>
         </is>
       </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Получить сырьё со склада «Проверка ОКК» можно после решения ОКК о его соответствии:
+1. Дождаться завершения контроля сырья сотрудником ОКК.
+2. После соответствия требованиям сотрудник ОКК по электронной почте информирует Руководителя ОКК, ответственных сотрудников бухгалтерии, Начальника СО и оператора склада с просьбой переместить сырьё со склада «На проверке ОКК» на соответствующий склад.
+3. После перемещения получить сырьё с обычного склада в установленном порядке.
+Решение о соответствии или несоответствии сырья принимает Руководитель ОКК / Директор по качеству. Самостоятельная выдача сырья технологу непосредственно со склада «Проверка ОКК» в источнике не предусмотрена.
+Источники: ПР-09-00-14 «Контроль качества»; ПР-03-00-12 «Несоответствующая продукция».</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1764,6 +1933,12 @@
           <t>ИСПРАВЛЕНО на ЭКО_2 (n=1/1 на тот момент)</t>
         </is>
       </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>В доступных источниках не нашёл порядка определения очередности выполнения нескольких срочных заявок на ремонт механиком.
+Источник найденного поиска — документы по корректировке заказов в 1С; они не описывают приоритизацию ремонтных заявок.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1822,6 +1997,13 @@
           <t>Без изменений — верно + аномалия</t>
         </is>
       </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Если поступило несколько заявок на обслуживание, первой выполняется заявка, неисправность по которой может повлиять на безопасность выпускаемой продукции.
+Приоритетность определяет Начальник ПУ и/или Мастер ПО. Заявки выполняет сотрудник РМС, назначенный Старшим механиком.
+Источник: ПР-10(02)-00/01 «Ремонтно-механическая служба»: «В случае наличия нескольких заявок на обслуживание приоритет отдается тем, которые способны оказать влияние на безопасность выпускаемой продукции. Приоритетность определяет Начальник ПУ и/или Мастер ПО».</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1880,6 +2062,17 @@
           <t>Без изменений — верно</t>
         </is>
       </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>При выпуске продукции с меньшим весом нужно сделать запас продукции на склад с учётом текущей загруженности оборудования:
+1. Проверьте отчёт «Планирование наработки на склад».
+2. Проверьте «Отчёт о загруженности оборудования» — он показывает статус оборудования по заказам и контрагентам.
+3. Учтите срочный заказ покупателя при составлении очередности производства; в найденном фрагменте отдельный порядок переприоритизации или остановки срочного заказа не установлен.
+4. Если потребность в запасе сформирована руководством, она передаётся Начальнику ПО запиской по электронной почте.
+5. Наработку на склад планируйте для товарных позиций с отметкой «не подлежит частичному резервированию».
+Источник: И-08-08-01 «Наработка складских позиций», файл для теста ИИ (1)/И-08-08-01 Наработка складских позиций.docx: «ПО планирует и осуществляет наработку складских позиций» на основании отчётов «планирование наработки на склад» и «Отчёт о загруженности оборудования»; потребность может быть передана Начальнику ПО руководством Компании.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1938,6 +2131,24 @@
           <t>Без изменений — ошибка сохраняется</t>
         </is>
       </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Действия оператора ПО при фасовке готовой продукции:
+Перед фасовкой
+1. Проверить в «Рабочей инструкции на производство» (форма 16-03): поле «Примечания к тех. процессу» — дополнительные этикетки, специальные знаки и другая важная информация; поле «Вид фасовки» — характеристики номенклатуры, в которые нужно расфасовать продукцию.
+2. Осмотреть тару или упаковку: проверить её количество, качество, чистоту и целостность.
+3. Не выполнять фасовку на полу: минимальное расстояние от пола — 10 см.
+Источник: И-08-02-10 «Фасовка и упаковка готовой продукции», п. 3.1.1–3.1.2 и фрагмент раздела 3.3.
+В процессе и после фасовки
+4. После фасовки закрыть тару: канистру закрутить пробкой до характерного «щелчка» либо закрыть крышкой и простучать киянкой; при нарушении кольца, отсутствии полимерного вкладыша или перекосе пробки/крышки установить новую крышку.
+5. При фасовке порошковых форм упаковать пакет в соответствии с видом упаковки, указанным в форме 16-03: запаять пакеты размеров 20×35, 35×50, 40×80 и все металлизированные пакеты; пакет размера 80×110 затянуть хомутом.
+6. При обнаружении брака упаковки выполнить перефасовку. Если обнаружено несколько единиц бракованной упаковки — уведомить Мастера ПО/Технолога ПО/Начальника ПУ.
+7. После завершения фасовки заполнить в форме 16-03: «Кол-во тарных мест» — фактическое количество расфасованного продукта в штуках по каждому виду характеристики; «Общее количество» — фактическое количество готового продукта в килограммах; «Дата» — дату окончания фасовки; «Фасовщик ФИО подпись» — ФИО и подпись фасовавшего сотрудника.
+8. Вывезти этикированную готовую продукцию на паллете в зону передачи готовой продукции на склад.
+9. Передать ответственному сотруднику ПО полностью заполненную форму 16-03 с фактическим количеством расфасованной продукции.
+Источники: И-08-02-10, разделы 3-4; ПР-08-00-14 «Производственный процесс», п. 5.6.3 и 5.7.1.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1996,6 +2207,16 @@
           <t>ИСПРАВЛЕНО на ЭКО_2 (n=2/2)</t>
         </is>
       </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Если утверждённой спецификации для нужной характеристики готовой продукции нет, ответственный сотрудник ПО должен:
+1. Направить запрос по электронной почте Ведущему технологу ПО.
+2. Поставить в копию Технического директора / Начальника ПО.
+3. Ведущий технолог ПО в течение одного рабочего дня вносит спецификацию для всех имеющихся характеристик номенклатуры.
+Подробный порядок самостоятельного добавления спецификации в интерфейсе 1С-8 в доступном фрагменте не приведён.
+Источник: Д-08-03-01 «Формирование заказов на производство в базе 1С-8», п. 3.6.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2052,6 +2273,20 @@
       <c r="L26" s="11" t="inlineStr">
         <is>
           <t>Без изменений — верно + аномалия (пустая карточка)</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Новую спецификацию в 1С-8 вносит ответственный сотрудник ПО на основании утверждённой «Рабочей инструкции на производство» (форма 16-03).
+Порядок:
+1. Получить утверждённую форму 16-03. Она должна быть утверждена руководителем ЛР / НИМРП / НА либо Техническим директором / Ведущим технологом.
+2. Внести спецификацию в базу 1С-8 в течение одного рабочего дня с момента получения утверждённой формы.
+3. В поле «Статья затрат» выбрать: «Сырье и материалы» — для сырья и товарных компонентов; «Канистры, пробки» — для тары и пакетов; «Этикетки, технологическая информация» — для этикеток.
+4. На вкладке «Дополнительно» установить: «Состояние» — «Утверждён»; «Дата утверждения» — заполняется автоматически; «Ответственный» — заполняется автоматически; «Назначение» — выбрать соответствующее значение: «В состав входит продукция», «Фасовка», «Ароматизаторы НА» либо оставить поле незаполненным, если эти варианты не применяются.
+5. Установить спецификацию как активную.
+6. Во вкладке «Файлы» прикрепить утверждённую форму 16-03: нажать «Добавить»; прикрепить рабочую инструкцию; в поле «Тип документа» выбрать «Документ по продукту».
+7. Нажать «Записать».
+Источник: И-08-05/08 «Внесение спецификаций в базе 1С-8», разделы «Основание для внесения спецификаций», «Порядок внесения спецификаций» и «На вкладке "Дополнительно"».</t>
         </is>
       </c>
     </row>

--- a/docs/accounts/eco/pilot-test-03-eco2-tracking.xlsx
+++ b/docs/accounts/eco/pilot-test-03-eco2-tracking.xlsx
@@ -2301,7 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2395,90 +2395,80 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Условия теста — заполнить по факту (см. instrukciya-test-eko-2.md, §6)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
+          <t>Условия теста (фактические, 12.09.2026)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Параметр</t>
+          <t>Модель</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Проход A / Проход B</t>
+          <t>OpenAI/gpt-5.5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Дата и время</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr"/>
+          <t>Агент</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Синапс.Инсайт — Closed-book RAG (системный) — основной; точечные вопросы также задавались агентом «Аналитик (планировщик)» в §1a для сравнения</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr"/>
+          <t>Рассуждения (reasoning)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Выключены</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Агент/режим</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr"/>
+          <t>Область поиска — источники</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Данные (каталог и SQL) + Документы; часть вопросов — только Документы (SQL/каталог выключен), см. протокол</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Рассуждения (reasoning)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr"/>
+          <t>Область поиска — коллекции</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Основной прогон — только «ЭКО»; точечные перепроверки — переключение на «ЭКО_2» (см. колонку «Коллекция»)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Область поиска — источники</t>
+          <t>Периметр</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>A: Данные (каталог и SQL) + Документы  |  B: только Документы</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Область поиска — коллекции</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Сузить до «ЭКО_2» в обоих проходах</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Обновлено 12.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Полный прогон 18/18 вопросов выполнен, коллекция ЭКО (Closed-book RAG системный), с точечными перепроверками на ЭКО_2 для 1.3/2.2/3.2/4.1/5.2/6.2. Подробности — pilot-test-03-eco2-protocol.md.</t>
+          <t>Бейдж «защищённый контур — данные не покидают компании»</t>
         </is>
       </c>
     </row>
